--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -110,6 +110,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -141,6 +142,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -176,6 +178,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -184,14 +187,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>发货组织</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.deliveryOrgName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>销售组织</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -231,6 +226,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -266,6 +262,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -297,6 +294,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -313,11 +311,20 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>库存组织</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.warehouseOrgName}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -326,7 +333,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -438,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -757,10 +764,10 @@
         <v>28</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>2</v>
@@ -769,19 +776,19 @@
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="O1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>4</v>
@@ -825,10 +832,10 @@
         <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>13</v>
@@ -837,22 +844,22 @@
         <v>14</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>16</v>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -123,6 +123,14 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>作废状态</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{.</t>
     </r>
@@ -135,7 +143,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>typeName</t>
+      <t>customerName</t>
     </r>
     <r>
       <rPr>
@@ -151,11 +159,23 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>作废状态</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户</t>
+    <t>销售组织</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.salesOrgName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>应发数量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.planQty}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>实发数量</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -171,7 +191,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>customerName</t>
+      <t>actualQty</t>
     </r>
     <r>
       <rPr>
@@ -187,23 +207,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>销售组织</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.salesOrgName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>应发数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.planQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>实发数量</t>
+    <t>库存单位</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>出货仓库</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -219,7 +227,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>actualQty</t>
+      <t>warehouseName</t>
     </r>
     <r>
       <rPr>
@@ -235,11 +243,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>库存单位</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>出货仓库</t>
+    <t>出库日期</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -255,7 +259,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>warehouseName</t>
+      <t>actualDeliveryDate</t>
     </r>
     <r>
       <rPr>
@@ -271,23 +275,8 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>出库日期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>actualDeliveryDate</t>
+    <r>
+      <t>{.planDeliveryDate</t>
     </r>
     <r>
       <rPr>
@@ -303,28 +292,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>{.planDeliveryDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>库存组织</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>{.warehouseOrgName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.orderTypeName}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -758,16 +734,16 @@
         <v>1</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>2</v>
@@ -776,19 +752,19 @@
         <v>3</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>4</v>
@@ -820,7 +796,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
@@ -829,13 +805,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>13</v>
@@ -844,22 +820,22 @@
         <v>14</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>16</v>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,20 +14,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>出库单号</t>
+  </si>
   <si>
     <t>销售单号</t>
   </si>
   <si>
+    <t>发货通知单号</t>
+  </si>
+  <si>
+    <t>单据类型</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
+    <t>作废状态</t>
+  </si>
+  <si>
+    <t>客户</t>
+  </si>
+  <si>
+    <t>收货国家</t>
+  </si>
+  <si>
+    <t>销售员</t>
+  </si>
+  <si>
+    <t>库存组织</t>
+  </si>
+  <si>
+    <t>销售组织</t>
+  </si>
+  <si>
     <t>sku</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
+    <t>应发数量</t>
+  </si>
+  <si>
+    <t>实发数量</t>
+  </si>
+  <si>
+    <t>库存单位</t>
+  </si>
+  <si>
+    <t>出货仓库</t>
+  </si>
+  <si>
+    <t>出库日期</t>
+  </si>
+  <si>
     <t>预计发货日期</t>
   </si>
   <si>
@@ -49,49 +91,17 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.invalidStatusName}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.unit}</t>
-  </si>
-  <si>
-    <t>{.packDate}</t>
-  </si>
-  <si>
-    <t>{.actualDeliveryDate}</t>
-  </si>
-  <si>
-    <t>{.approveUserName}</t>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>出库单号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>{.soCode}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>发货通知单号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.</t>
     </r>
     <r>
@@ -99,7 +109,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -110,28 +119,54 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>单据类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>作废状态</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.orderTypeName}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.customerName}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
+  </si>
+  <si>
+    <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.warehouseOrgName}</t>
+  </si>
+  <si>
+    <t>{.salesOrgName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.planQty}</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.</t>
     </r>
     <r>
@@ -139,55 +174,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customerName</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>销售组织</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.salesOrgName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>应发数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.planQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>实发数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -198,24 +184,24 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>库存单位</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>出货仓库</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unit}</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.</t>
     </r>
     <r>
@@ -223,7 +209,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -234,20 +219,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>出库日期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.</t>
     </r>
     <r>
@@ -255,7 +241,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -266,16 +251,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>{.planDeliveryDate</t>
     </r>
     <r>
@@ -283,38 +273,50 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>库存组织</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.warehouseOrgName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.orderTypeName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.packDate}</t>
+  </si>
+  <si>
+    <t>{.actualDeliveryDate}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -331,46 +333,368 @@
       <sz val="10"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
-      <sz val="9.8000000000000007"/>
+      <sz val="9.8"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC7832"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -393,9 +717,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -403,32 +969,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -690,13 +1303,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -705,169 +1318,181 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
-    <col min="7" max="9" width="30.625" customWidth="1"/>
-    <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="11" width="27" customWidth="1"/>
-    <col min="12" max="13" width="15.125" customWidth="1"/>
-    <col min="14" max="14" width="11.875" customWidth="1"/>
-    <col min="15" max="15" width="25.625" customWidth="1"/>
-    <col min="16" max="16" width="21.25" customWidth="1"/>
-    <col min="17" max="18" width="21.125" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="22" width="20.625" customWidth="1"/>
+    <col min="7" max="11" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="14.75" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="14" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="17" max="17" width="25.625" customWidth="1"/>
+    <col min="18" max="18" width="21.25" customWidth="1"/>
+    <col min="19" max="20" width="21.125" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="24" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:24">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>9</v>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>20</v>
-      </c>
+    <row r="4" spans="6:6">
+      <c r="F4" s="3"/>
     </row>
-    <row r="4" spans="1:22">
-      <c r="F4" s="6"/>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4"/>
     </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="1"/>
+    <row r="8" spans="1:1">
+      <c r="A8" s="5"/>
     </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="3"/>
+    <row r="9" spans="1:1">
+      <c r="A9" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="24225" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -226,36 +226,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>actualDeliveryDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
+    <t>{.billDate}</t>
   </si>
   <si>
     <r>
@@ -298,7 +269,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -306,17 +277,10 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -356,6 +320,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -369,6 +361,14 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -413,14 +413,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -428,7 +421,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -436,6 +429,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -444,57 +444,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -509,13 +473,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,24 +539,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -569,18 +587,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -593,36 +599,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -641,24 +623,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -672,12 +642,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,6 +678,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -747,21 +726,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -820,225 +784,222 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1334,7 +1295,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1343,7 +1304,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1364,10 +1325,10 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1385,27 +1346,27 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1417,10 +1378,10 @@
       <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1438,10 +1399,10 @@
       <c r="K2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -1450,7 +1411,7 @@
       <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>39</v>
       </c>
       <c r="Q2" s="1" t="s">
@@ -1462,33 +1423,33 @@
       <c r="S2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="6:6">
-      <c r="F4" s="3"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="6"/>
+      <c r="A9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>出库单号</t>
   </si>
   <si>
+    <t>物流单号</t>
+  </si>
+  <si>
     <t>销售单号</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.soCode}</t>
@@ -269,7 +275,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -320,55 +326,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -413,6 +383,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -458,7 +443,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,49 +479,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,121 +617,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,21 +684,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -726,6 +717,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -784,148 +790,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -954,52 +960,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1270,28 +1276,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" width="18.125" customWidth="1"/>
-    <col min="7" max="11" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="14.75" customWidth="1"/>
-    <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="15" width="15.125" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
-    <col min="17" max="17" width="25.625" customWidth="1"/>
-    <col min="18" max="18" width="21.25" customWidth="1"/>
-    <col min="19" max="20" width="21.125" customWidth="1"/>
-    <col min="21" max="21" width="21" customWidth="1"/>
-    <col min="22" max="24" width="20.625" customWidth="1"/>
+    <col min="1" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="8" max="12" width="30.625" customWidth="1"/>
+    <col min="13" max="13" width="14.75" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="11.875" customWidth="1"/>
+    <col min="18" max="18" width="25.625" customWidth="1"/>
+    <col min="19" max="19" width="21.25" customWidth="1"/>
+    <col min="20" max="21" width="21.125" customWidth="1"/>
+    <col min="22" max="22" width="21" customWidth="1"/>
+    <col min="23" max="25" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1364,92 +1370,101 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="Q2" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="R2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="6:6">
-      <c r="F4" s="2"/>
+    <row r="4" spans="7:7">
+      <c r="G4" s="2"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2">
       <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:2">
       <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:2">
       <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>出库单号</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>收货国家</t>
+  </si>
+  <si>
+    <t>客户订单号</t>
   </si>
   <si>
     <t>销售员</t>
@@ -145,6 +148,9 @@
   </si>
   <si>
     <t>{.countryName}</t>
+  </si>
+  <si>
+    <t>{.customerOrderNo}</t>
   </si>
   <si>
     <t>{.sellerName}</t>
@@ -1276,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1285,19 +1291,19 @@
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="18.125" customWidth="1"/>
-    <col min="8" max="12" width="30.625" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="27" customWidth="1"/>
-    <col min="15" max="16" width="15.125" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="25.625" customWidth="1"/>
-    <col min="19" max="19" width="21.25" customWidth="1"/>
-    <col min="20" max="21" width="21.125" customWidth="1"/>
-    <col min="22" max="22" width="21" customWidth="1"/>
-    <col min="23" max="25" width="20.625" customWidth="1"/>
+    <col min="8" max="13" width="30.625" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="16" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="25.625" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="22" width="21.125" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="26" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1373,82 +1379,88 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="R2" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="S2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>出库单号</t>
   </si>
@@ -105,6 +105,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -115,6 +116,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -125,6 +127,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -170,6 +173,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -180,6 +184,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -190,6 +195,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -205,6 +211,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -215,6 +222,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -225,6 +233,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -240,6 +249,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -250,6 +260,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -270,20 +281,24 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>销售员部门</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.salesDeptName}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -303,368 +318,46 @@
       <sz val="10"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="9.8"/>
+      <sz val="9.8000000000000007"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC7832"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -687,255 +380,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -954,61 +405,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1270,13 +677,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1285,19 +692,19 @@
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="18.125" customWidth="1"/>
-    <col min="8" max="12" width="30.625" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="27" customWidth="1"/>
-    <col min="15" max="16" width="15.125" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="25.625" customWidth="1"/>
-    <col min="19" max="19" width="21.25" customWidth="1"/>
-    <col min="20" max="21" width="21.125" customWidth="1"/>
-    <col min="22" max="22" width="21" customWidth="1"/>
-    <col min="23" max="25" width="20.625" customWidth="1"/>
+    <col min="8" max="13" width="30.625" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="16" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="25.625" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="22" width="21.125" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="26" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1328,53 +735,56 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1405,70 +815,73 @@
       <c r="J2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="7:7">
+    <row r="4" spans="1:26">
       <c r="G4" s="2"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:26">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:26">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:26">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>出库单号</t>
   </si>
@@ -288,6 +288,14 @@
   </si>
   <si>
     <t>{.salesDeptName}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.customerOrderNo}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>客户订单号</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -296,7 +304,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -405,7 +413,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -683,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -692,19 +700,19 @@
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="18.125" customWidth="1"/>
-    <col min="8" max="13" width="30.625" customWidth="1"/>
-    <col min="14" max="14" width="14.75" customWidth="1"/>
-    <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="17" width="15.125" customWidth="1"/>
-    <col min="18" max="18" width="11.875" customWidth="1"/>
-    <col min="19" max="19" width="25.625" customWidth="1"/>
-    <col min="20" max="20" width="21.25" customWidth="1"/>
-    <col min="21" max="22" width="21.125" customWidth="1"/>
-    <col min="23" max="23" width="21" customWidth="1"/>
-    <col min="24" max="26" width="20.625" customWidth="1"/>
+    <col min="8" max="14" width="30.625" customWidth="1"/>
+    <col min="15" max="15" width="14.75" customWidth="1"/>
+    <col min="16" max="16" width="27" customWidth="1"/>
+    <col min="17" max="18" width="15.125" customWidth="1"/>
+    <col min="19" max="19" width="11.875" customWidth="1"/>
+    <col min="20" max="20" width="25.625" customWidth="1"/>
+    <col min="21" max="21" width="21.25" customWidth="1"/>
+    <col min="22" max="23" width="21.125" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1"/>
+    <col min="25" max="27" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,62 +737,65 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -809,73 +820,76 @@
       <c r="H2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="G4" s="2"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>出库单号</t>
   </si>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售单价</t>
+  </si>
+  <si>
+    <t>销售单价(本位币)</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>含税单价(本位币)</t>
+  </si>
+  <si>
+    <t>价税合计(本位币)</t>
   </si>
   <si>
     <t>应发数量</t>
@@ -166,6 +181,21 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.price}</t>
+  </si>
+  <si>
+    <t>{.cnyPrice}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxAmount}</t>
   </si>
   <si>
     <t>{.planQty}</t>
@@ -1282,7 +1312,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1293,17 +1323,17 @@
     <col min="7" max="7" width="18.125" customWidth="1"/>
     <col min="8" max="13" width="30.625" customWidth="1"/>
     <col min="14" max="14" width="14.75" customWidth="1"/>
-    <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="17" width="15.125" customWidth="1"/>
-    <col min="18" max="18" width="11.875" customWidth="1"/>
-    <col min="19" max="19" width="25.625" customWidth="1"/>
-    <col min="20" max="20" width="21.25" customWidth="1"/>
-    <col min="21" max="22" width="21.125" customWidth="1"/>
-    <col min="23" max="23" width="21" customWidth="1"/>
-    <col min="24" max="26" width="20.625" customWidth="1"/>
+    <col min="15" max="20" width="27" customWidth="1"/>
+    <col min="21" max="22" width="15.125" customWidth="1"/>
+    <col min="23" max="23" width="11.875" customWidth="1"/>
+    <col min="24" max="24" width="25.625" customWidth="1"/>
+    <col min="25" max="25" width="21.25" customWidth="1"/>
+    <col min="26" max="27" width="21.125" customWidth="1"/>
+    <col min="28" max="28" width="21" customWidth="1"/>
+    <col min="29" max="31" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,85 +1412,115 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>出库单号</t>
   </si>
@@ -40,12 +40,18 @@
     <t>客户</t>
   </si>
   <si>
+    <t>客户订单号</t>
+  </si>
+  <si>
     <t>收货国家</t>
   </si>
   <si>
     <t>销售员</t>
   </si>
   <si>
+    <t>销售员部门</t>
+  </si>
+  <si>
     <t>库存组织</t>
   </si>
   <si>
@@ -56,6 +62,21 @@
   </si>
   <si>
     <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售单价</t>
+  </si>
+  <si>
+    <t>销售单价(本位币)</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>含税单价(本位币)</t>
+  </si>
+  <si>
+    <t>价税合计(本位币)</t>
   </si>
   <si>
     <t>应发数量</t>
@@ -105,7 +126,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -116,7 +136,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -127,7 +146,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -147,12 +165,18 @@
     <t>{.customerName}</t>
   </si>
   <si>
+    <t>{.customerOrderNo}</t>
+  </si>
+  <si>
     <t>{.countryName}</t>
   </si>
   <si>
     <t>{.sellerName}</t>
   </si>
   <si>
+    <t>{.salesDeptName}</t>
+  </si>
+  <si>
     <t>{.warehouseOrgName}</t>
   </si>
   <si>
@@ -163,6 +187,21 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.price}</t>
+  </si>
+  <si>
+    <t>{.cnyPrice}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxAmount}</t>
   </si>
   <si>
     <t>{.planQty}</t>
@@ -173,7 +212,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -184,7 +222,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -195,7 +232,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -211,7 +247,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -222,7 +257,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -233,7 +267,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -249,7 +282,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -260,7 +292,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -282,31 +313,19 @@
   <si>
     <t>{.createTime}</t>
   </si>
-  <si>
-    <t>销售员部门</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.salesDeptName}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.customerOrderNo}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>客户订单号</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -326,46 +345,381 @@
       <sz val="10"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
-      <sz val="9.8000000000000007"/>
+      <sz val="9.8"/>
       <color rgb="FF629755"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC7832"/>
       <name val="JetBrains Mono"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -388,13 +742,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -413,17 +1009,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -685,13 +1331,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -702,17 +1348,17 @@
     <col min="7" max="7" width="18.125" customWidth="1"/>
     <col min="8" max="14" width="30.625" customWidth="1"/>
     <col min="15" max="15" width="14.75" customWidth="1"/>
-    <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="18" width="15.125" customWidth="1"/>
-    <col min="19" max="19" width="11.875" customWidth="1"/>
-    <col min="20" max="20" width="25.625" customWidth="1"/>
-    <col min="21" max="21" width="21.25" customWidth="1"/>
-    <col min="22" max="23" width="21.125" customWidth="1"/>
-    <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="27" width="20.625" customWidth="1"/>
+    <col min="16" max="21" width="27" customWidth="1"/>
+    <col min="22" max="23" width="15.125" customWidth="1"/>
+    <col min="24" max="24" width="11.875" customWidth="1"/>
+    <col min="25" max="25" width="25.625" customWidth="1"/>
+    <col min="26" max="26" width="21.25" customWidth="1"/>
+    <col min="27" max="28" width="21.125" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="32" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,165 +1383,195 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>24</v>
+      <c r="W2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="7:7">
       <c r="G4" s="2"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>出库单号</t>
   </si>
@@ -40,18 +40,15 @@
     <t>客户</t>
   </si>
   <si>
+    <t>收货国家</t>
+  </si>
+  <si>
     <t>客户订单号</t>
   </si>
   <si>
-    <t>收货国家</t>
-  </si>
-  <si>
     <t>销售员</t>
   </si>
   <si>
-    <t>销售员部门</t>
-  </si>
-  <si>
     <t>库存组织</t>
   </si>
   <si>
@@ -62,21 +59,6 @@
   </si>
   <si>
     <t>产品名称</t>
-  </si>
-  <si>
-    <t>销售单价</t>
-  </si>
-  <si>
-    <t>销售单价(本位币)</t>
-  </si>
-  <si>
-    <t>含税单价</t>
-  </si>
-  <si>
-    <t>含税单价(本位币)</t>
-  </si>
-  <si>
-    <t>价税合计(本位币)</t>
   </si>
   <si>
     <t>应发数量</t>
@@ -165,18 +147,15 @@
     <t>{.customerName}</t>
   </si>
   <si>
+    <t>{.countryName}</t>
+  </si>
+  <si>
     <t>{.customerOrderNo}</t>
   </si>
   <si>
-    <t>{.countryName}</t>
-  </si>
-  <si>
     <t>{.sellerName}</t>
   </si>
   <si>
-    <t>{.salesDeptName}</t>
-  </si>
-  <si>
     <t>{.warehouseOrgName}</t>
   </si>
   <si>
@@ -187,21 +166,6 @@
   </si>
   <si>
     <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.price}</t>
-  </si>
-  <si>
-    <t>{.cnyPrice}</t>
-  </si>
-  <si>
-    <t>{.taxPrice}</t>
-  </si>
-  <si>
-    <t>{.cnyTaxPrice}</t>
-  </si>
-  <si>
-    <t>{.cnyTaxAmount}</t>
   </si>
   <si>
     <t>{.planQty}</t>
@@ -325,7 +289,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -358,19 +322,6 @@
       <sz val="10"/>
       <color rgb="FFCC7832"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -845,19 +796,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -866,131 +826,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1008,12 +959,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1346,19 +1291,19 @@
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="18.125" customWidth="1"/>
-    <col min="8" max="14" width="30.625" customWidth="1"/>
-    <col min="15" max="15" width="14.75" customWidth="1"/>
-    <col min="16" max="21" width="27" customWidth="1"/>
-    <col min="22" max="23" width="15.125" customWidth="1"/>
-    <col min="24" max="24" width="11.875" customWidth="1"/>
-    <col min="25" max="25" width="25.625" customWidth="1"/>
-    <col min="26" max="26" width="21.25" customWidth="1"/>
-    <col min="27" max="28" width="21.125" customWidth="1"/>
-    <col min="29" max="29" width="21" customWidth="1"/>
-    <col min="30" max="32" width="20.625" customWidth="1"/>
+    <col min="8" max="13" width="30.625" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="16" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="25.625" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="22" width="21.125" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="26" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1328,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1392,7 +1337,7 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1407,7 +1352,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -1437,121 +1382,85 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="O2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>出库单号</t>
   </si>
@@ -59,21 +59,6 @@
   </si>
   <si>
     <t>产品名称</t>
-  </si>
-  <si>
-    <t>销售单价</t>
-  </si>
-  <si>
-    <t>销售单价(本位币)</t>
-  </si>
-  <si>
-    <t>含税单价</t>
-  </si>
-  <si>
-    <t>含税单价(本位币)</t>
-  </si>
-  <si>
-    <t>价税合计(本位币)</t>
   </si>
   <si>
     <t>应发数量</t>
@@ -181,21 +166,6 @@
   </si>
   <si>
     <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.price}</t>
-  </si>
-  <si>
-    <t>{.cnyPrice}</t>
-  </si>
-  <si>
-    <t>{.taxPrice}</t>
-  </si>
-  <si>
-    <t>{.cnyTaxPrice}</t>
-  </si>
-  <si>
-    <t>{.cnyTaxAmount}</t>
   </si>
   <si>
     <t>{.planQty}</t>
@@ -1312,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1323,17 +1293,17 @@
     <col min="7" max="7" width="18.125" customWidth="1"/>
     <col min="8" max="13" width="30.625" customWidth="1"/>
     <col min="14" max="14" width="14.75" customWidth="1"/>
-    <col min="15" max="20" width="27" customWidth="1"/>
-    <col min="21" max="22" width="15.125" customWidth="1"/>
-    <col min="23" max="23" width="11.875" customWidth="1"/>
-    <col min="24" max="24" width="25.625" customWidth="1"/>
-    <col min="25" max="25" width="21.25" customWidth="1"/>
-    <col min="26" max="27" width="21.125" customWidth="1"/>
-    <col min="28" max="28" width="21" customWidth="1"/>
-    <col min="29" max="31" width="20.625" customWidth="1"/>
+    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="16" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="25.625" customWidth="1"/>
+    <col min="20" max="20" width="21.25" customWidth="1"/>
+    <col min="21" max="22" width="21.125" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="26" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,115 +1382,85 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>出库单号</t>
   </si>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售单价</t>
+  </si>
+  <si>
+    <t>销售单价（本位币）</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>含税单价（本位币）</t>
+  </si>
+  <si>
+    <t>价税合计（本位币）</t>
   </si>
   <si>
     <t>应发数量</t>
@@ -166,6 +181,21 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.price}</t>
+  </si>
+  <si>
+    <t>{.cnyPrice}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxPrice}</t>
+  </si>
+  <si>
+    <t>{.cnyTaxAmount}</t>
   </si>
   <si>
     <t>{.planQty}</t>
@@ -1282,7 +1312,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1293,17 +1323,17 @@
     <col min="7" max="7" width="18.125" customWidth="1"/>
     <col min="8" max="13" width="30.625" customWidth="1"/>
     <col min="14" max="14" width="14.75" customWidth="1"/>
-    <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="17" width="15.125" customWidth="1"/>
-    <col min="18" max="18" width="11.875" customWidth="1"/>
-    <col min="19" max="19" width="25.625" customWidth="1"/>
-    <col min="20" max="20" width="21.25" customWidth="1"/>
-    <col min="21" max="22" width="21.125" customWidth="1"/>
-    <col min="23" max="23" width="21" customWidth="1"/>
-    <col min="24" max="26" width="20.625" customWidth="1"/>
+    <col min="15" max="20" width="27" customWidth="1"/>
+    <col min="21" max="22" width="15.125" customWidth="1"/>
+    <col min="23" max="23" width="11.875" customWidth="1"/>
+    <col min="24" max="24" width="25.625" customWidth="1"/>
+    <col min="25" max="25" width="21.25" customWidth="1"/>
+    <col min="26" max="27" width="21.125" customWidth="1"/>
+    <col min="28" max="28" width="21" customWidth="1"/>
+    <col min="29" max="31" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,85 +1412,115 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="7:7">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -195,7 +195,7 @@
     <t>{.cnyTaxPrice}</t>
   </si>
   <si>
-    <t>{.cnyTaxAmount}</t>
+    <t>{.allAmountLocalCurrency}</t>
   </si>
   <si>
     <t>{.planQty}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -9,12 +9,25 @@
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>出库单号</t>
   </si>
@@ -25,6 +38,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>第三方单据编号</t>
+  </si>
+  <si>
     <t>发货通知单号</t>
   </si>
   <si>
@@ -116,6 +132,9 @@
   </si>
   <si>
     <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.thirdCode}</t>
   </si>
   <si>
     <r>
@@ -311,7 +330,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1312,28 +1331,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="18.125" customWidth="1"/>
-    <col min="8" max="13" width="30.625" customWidth="1"/>
-    <col min="14" max="14" width="14.75" customWidth="1"/>
-    <col min="15" max="20" width="27" customWidth="1"/>
-    <col min="21" max="22" width="15.125" customWidth="1"/>
-    <col min="23" max="23" width="11.875" customWidth="1"/>
-    <col min="24" max="24" width="25.625" customWidth="1"/>
-    <col min="25" max="25" width="21.25" customWidth="1"/>
-    <col min="26" max="27" width="21.125" customWidth="1"/>
-    <col min="28" max="28" width="21" customWidth="1"/>
-    <col min="29" max="31" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="9" max="14" width="30.625" customWidth="1"/>
+    <col min="15" max="15" width="14.75" customWidth="1"/>
+    <col min="16" max="21" width="27" customWidth="1"/>
+    <col min="22" max="23" width="15.125" customWidth="1"/>
+    <col min="24" max="24" width="11.875" customWidth="1"/>
+    <col min="25" max="25" width="25.625" customWidth="1"/>
+    <col min="26" max="26" width="21.25" customWidth="1"/>
+    <col min="27" max="28" width="21.125" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="32" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,104 +1446,110 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="X2" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="Y2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="4" spans="7:7">
-      <c r="G4" s="2"/>
+    <row r="4" spans="8:8">
+      <c r="H4" s="2"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.trackNo}</t>
+    <t>{.trackNos}</t>
   </si>
   <si>
     <t>{.soCode}</t>
